--- a/Pulse_Economy_V5.xlsx
+++ b/Pulse_Economy_V5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bot_2\telegram_bot2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB63E1-60C0-4120-BDC1-A3B6B015065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEBDE7-3490-4F15-819A-DC683A0A1286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,8 +33,1463 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>илья клименко</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{23356265-DD12-426E-8705-BAF70CA4DE42}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+• : Любой текст длиннее 2 слов</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{FC83FE88-5064-4EB6-BB0D-7DCC933B9696}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправка одной фотографии.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{972DB3A5-9B8F-42F9-9CF7-C5E97AE4BC27}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Нажал Reply на чужое сообщение.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{7CB22FC6-8468-4603-B8FA-9A0283D2E781}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке КиноON. Использовать скрытый текст (телеграм-спойлер ||текст||).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{4DE63A04-565D-4197-8F7C-1AE95635BC44}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сообщение, состоящее только из смайлика</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{2B1A7FC4-26CC-4C16-BF42-26A0E90F0D9F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+• Отправка альбома (от 2 фото) в ветках типа ПИТОМЦЫ.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{A843A253-21E4-4188-9A5E-B20ECA17A854}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Кто-то сделал Reply на твое сообщение (начисляется тебе задним числом).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{B1EF1A75-3877-4AFF-8C74-6DC8E155132A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке Встречи. Написать сообщение, содержащее маркеры времени (сегодня, завтра) и точное время (например, 19:30).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{2D2E8037-46DA-4D11-A0BE-BF11F961FD24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Загрузка обычного видеофайла.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{9A6177FC-FD7A-4921-A1FC-B8E6590A87E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Ты нажал на любую реакцию.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{405A778B-048A-4BF0-B172-E0E9C6424AEA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Запись Video Note (кружочка) с камеры. Самая дорогая база, т.к. требует личного участия.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{11587EFF-9898-49DD-A3B1-44CD0AE238D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Кто-то поставил реакцию на твой пост (начисляется тебе задним числом).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{6179498D-73CC-40F7-8EE1-2323B35847DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Написал текст длиннее 50 символов.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{762317F4-469A-43AF-A8D4-F0594FC716A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправка URL-ссылки или аудиофайла.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{6C916296-2A7D-4870-B3C4-6204A04A6D68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке ЗадротыON. Отметить через @ сразу трех и более разных людей в одном сообщении.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{36EAA1F8-00A5-4691-8D79-1079A461D484}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Запись голосового сообщения.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{5AF1D8BA-ED33-4392-817A-E62308A5A13D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке НьюзON. Отправить ссылку + свой авторский текст длиннее 20 слов.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{ADA3B5AD-E585-44FE-89E2-96E09FB0334C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправка гифки.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{08B34591-CF00-4F04-A722-9BEF12866ECE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+]: На твое сообщение ответили (Reply) больше 2 раз разные люди.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{87B304FA-D0AB-4044-ACED-46F09E9C4EE9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Написать 10 сообщений за сутки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{3A06F269-0FC6-46DB-9243-6244EF5AA6F6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Твое сообщение собрало 3 лайка.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{66E89BE7-892A-4320-9852-39060441780D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить 10 отдельных эмодзи за сутки.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{27C8716A-11E7-46E8-BD5A-71D94E661683}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Твое сообщение собрало 4 лайка.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{C8907BC2-69D1-4425-A8AC-2F083CE6311A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке ПлюсON (Здоровье). Написать развернутый ответ (&gt;15 слов) на чужой вопрос в период с 02:00 до 06:00 по МСК.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{C8E72B8E-0F75-4751-B18F-2691829AD111}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Прикрепил фото + написал текст длиннее 50 символов в одном сообщении.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{494756C7-DA79-4D34-9561-54A11FDAF07D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Твое сообщение собрало 6 и более лайков.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{0AED470B-5F61-4ED4-80A5-B4997FC35A60}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+• Суть: Если пользователь ставит реакцию ❤️ или 🔥 на 3 разные анкеты в течение 24 часов, он получает награду. Это стимулирует людей листать анкеты и поддерживать авторов.
+• Награда: + 20 💎 (Коэф: 10000).
+• Частота: 1 раз в 24 часа.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{16534D3C-A916-46B6-AB2B-B26713E4F985}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Прикрепил видео + написал текст длиннее 100 слов.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{2891F49F-6EA6-452B-8FDC-54867FAC4757}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить сообщение ровно в 11:11, 22:22, 00:00 или 12:34.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{6C94D9E7-A2C9-427E-8653-9B4DD14C059C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправил ссылку, которую бот распознал как плейлист (Spotify, Яндекс, VK Музыка).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{C36D8377-DBBC-4EF4-97D6-7DEC37D332B2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Написать самое первое сообщение в чате после 05:00 утра.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{72BBA486-C72B-43EF-A63F-0D5E60C24D0E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Ответить другим людям (Reply) 20 раз за час.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{4F9FCC4A-AF64-43CD-A64E-9DC32B6F150F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В любой ветке. Если 5 разных людей подряд отправляют одинаковый эмодзи (флешмоб) — бонус получают все пятеро.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{EF74682C-CF3D-46A3-8379-0FCD0E051797}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Написать мега-лонгрид длиннее 1000 символов (без ссылок).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{85FE4C0F-FD6E-4130-96B7-E724718196FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Получить 20 ответов на свои сообщения от других людей за полдня.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{E3513836-A028-4435-B637-00AAB12D3E07}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+В ветке МемасON. Картинка собрала 15+ лайков от разных людей за 1 час.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{7FCAC53A-6F63-4324-BEA9-E3BBB91BA9E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить ровно 100-е, 500-е или 1000-е сообщение в чате за текущие сутки.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{5389F454-C8BE-483D-B23B-3936669EDFE9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить 3 и более фото за сутки.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{162B195C-1461-4AAD-8106-791922F09734}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Поставить 5 лайков другим людям за час.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{C5429340-DD59-4849-A362-B28FB842D517}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Употребить в тексте случайно загаданное ботом слово недели (например, "кофе").</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{9750B388-6AA0-438C-BF21-47A89C526C59}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить 2 видео за сутки в спец. ветках (Животные, Кухарка, Задроты).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{737F441E-CDCD-40B3-95F8-5D21B5533526}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Получить 10 лайков на свои посты за час.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{9F52F8EB-CB84-408E-A432-842D46A6BD38}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Базовый 2% шанс при отправке любого сообщения сорвать джекпот (х10 к базе).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{626D1EF8-9615-406D-9050-27B674E538AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Записать 5 видео-кружков за полдня.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0" shapeId="0" xr:uid="{8D0216CB-874F-459B-8D49-4B61268FB1ED}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Бот дает подсказку в Главный чат. Нужно первым добежать до загаданной ветки и написать туда сообщение.
+Перебегушка» (Блуждающая Аномалия)
+Твоя идея с лягушкой, которая скачет по веткам — это абсолютный хит. Это создаст эффект FOMO (страх упущенной выгоды) и заставит людей заглядывать в те ветки, куда они обычно не заходят.
+Как это работает:
+Давай назовем ее «Блуждающий Пульс» (или Золотая Лягушка 🐸, как тебе больше нравится).
+1. Прыжок: Раз в несколько часов (рандомно) бот в тихую выбирает одну из веток форума. Например, ЗадротыON.
+2. Подсказка в Главный чат: Бот пишет в Главный чат загадку:
+"🐸 Ква! Золотая лягушка куда-то ускакала... Кажется, я слышал звуки джойстика и выстрелов..."
+3. Охота: Люди понимают — Лягушка в ветке ЗадротыON! Они бегут туда. Первые 3 человека, которые напишут любое сообщение в этой ветке, "ловят" лягушку.
+4. Награда: Бот отвечает им прямо в ветке: "🏆 @username поймал Золотую Лягушку и получает +50 💎!". После 3 поимок лягушка исчезает до следующего раза.
+🔥 ДЖЕКПОТ (Прыжок в Главный чат):
+Как ты и предложил, если рандом решает, что Лягушка прыгает в ЧатON (Главный чат без темы), случается Чудо.
+• Бот присылает огромную гифку сирены:
+🚨 ЗОЛОТАЯ ЛИХОРАДКА! Лягушка забежала в Главный Чат!
+В течение следующих 5 минут АБСОЛЮТНО ВСЕ сообщения здесь приносят х5 Пульсов! Время пошло!
+• Начинается абсолютное безумие, люди бросают свои дела и 5 минут активно общаются, фармя монеты. Через 5 минут бот пишет: "Лягушка устала и ушла спать. Лихорадка окончена".
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{E1B6CD0C-D4F1-4108-882F-DF0EEDD85B9E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Текст &gt;10 слов, содержащий "спасибо", "пожалуйста", "благодарю".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{8D260B48-35C2-4888-B7DC-578158F66A6F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить 5 треков/ссылок на музыку за сутки в ветке МузON.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{2838347E-9591-48D6-A91E-50AAA679F39C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Записать 4 голосовых сообщения за один час</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{D0832FF7-746C-4F05-A8A6-21C54D2D8A39}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сделать Reply на самое первое сообщение новичка в чате.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="0" shapeId="0" xr:uid="{A8A153E7-FC34-4EF4-9719-1430FBBE8C3A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправить 10 гифок за час (лимит спама гифками).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{B5C204A3-5A15-4C52-B976-5D1DB57A0917}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сделать Reply на чужое сообщение быстрее, чем за 10 секунд после его публикации.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{BB34015E-D125-47E7-A080-FF57FECBD685}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отправка абсолютно одинакового текста/гифки 2 раза за 1 час.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{F8711D71-472E-40CD-BADB-9B7B81DBF8F7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сделать Reply на сообщение, которое было отправлено более 48 часов назад (реанимация старых тем).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{3CB2D7C6-D0B5-4F64-B59C-98B8CEB7FE76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Нарушение логики ветки (например, отправка голого текста в МузON или МемасON). Обнуляет награду за текущее сообщение.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{AD8B3CCA-0370-4A69-A8E8-5B7E8D3C2953}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>илья клименко:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Сообщение пользователя было удалено модератором (или анти-мат ботом). Жесткий штраф.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
   <si>
     <t>ГЛОБАЛЬНАЯ БАЗА (1x) =</t>
   </si>
@@ -165,12 +1620,6 @@
     <t>Легенда (6+ лайков)</t>
   </si>
   <si>
-    <t>Сваха (BBS)</t>
-  </si>
-  <si>
-    <t>Неделя</t>
-  </si>
-  <si>
     <t>🎁 СЕКРЕТЫ (Пасхалки)</t>
   </si>
   <si>
@@ -298,6 +1747,59 @@
   </si>
   <si>
     <t>Биомы</t>
+  </si>
+  <si>
+    <t>«Амбассадор Любви»</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>ИВЕНТЫ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>1 Сезон - Биомы: Неслыханные легенды</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>🌍 БИОМЫ К ЭТОМУ ИВЕНТУ</t>
   </si>
 </sst>
 </file>
@@ -308,7 +1810,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.000\ \_xd83d_\_xdc8e_"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +1865,59 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -403,13 +1958,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +1996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -459,10 +2014,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -473,14 +2046,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -515,6 +2080,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr lang="ru-RU"/>
               <a:t>Источники дохода 💎</a:t>
             </a:r>
           </a:p>
@@ -941,14 +2507,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="2" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -964,17 +2530,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="1">
         <v>2E-3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="M1" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1004,8 +2575,8 @@
       <c r="K3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>7</v>
+      <c r="M3" s="15" t="s">
+        <v>88</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>3</v>
@@ -1015,26 +2586,26 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="E4" s="13" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="E4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="I4" s="13" t="s">
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="I4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="M4" s="13" t="s">
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="M4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1067,7 +2638,7 @@
       <c r="M5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="16">
         <v>1000</v>
       </c>
       <c r="O5" s="8" t="s">
@@ -1105,7 +2676,7 @@
       <c r="M6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="16">
         <v>1500</v>
       </c>
       <c r="O6" s="8" t="s">
@@ -1133,11 +2704,11 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
       <c r="E8" s="7" t="s">
         <v>24</v>
       </c>
@@ -1156,11 +2727,11 @@
       <c r="K8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1184,7 +2755,7 @@
       <c r="M9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="16">
         <v>4000</v>
       </c>
       <c r="O9" s="8" t="s">
@@ -1201,15 +2772,15 @@
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
       <c r="M10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="16">
         <v>5000</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -1217,11 +2788,11 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
       <c r="E11" s="7" t="s">
         <v>33</v>
       </c>
@@ -1260,11 +2831,11 @@
       <c r="K12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1276,11 +2847,11 @@
       <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
       <c r="I13" s="7" t="s">
         <v>39</v>
       </c>
@@ -1293,7 +2864,7 @@
       <c r="M13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="16">
         <v>12500</v>
       </c>
       <c r="O13" s="8" t="s">
@@ -1319,24 +2890,24 @@
       <c r="K14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="N14" s="20">
-        <v>0</v>
-      </c>
-      <c r="O14" s="20" t="s">
-        <v>44</v>
+      <c r="M14" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="N14" s="17">
+        <v>10000</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
       <c r="E15" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F15" s="8">
         <v>20</v>
@@ -1347,16 +2918,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="8">
+        <v>45</v>
+      </c>
+      <c r="B16" s="16">
         <v>5500</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="8">
         <v>15</v>
@@ -1364,63 +2935,63 @@
       <c r="G16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="M16" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="M16" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="8">
+        <v>48</v>
+      </c>
+      <c r="B17" s="16">
         <v>7500</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J17" s="8">
         <v>20</v>
       </c>
       <c r="K17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="16">
+        <v>25000</v>
+      </c>
+      <c r="O17" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="8">
-        <v>25000</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="8">
+        <v>53</v>
+      </c>
+      <c r="B18" s="16">
         <v>15000</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
       <c r="I18" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J18" s="8">
         <v>25</v>
@@ -1429,9 +3000,9 @@
         <v>15</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N18" s="8">
+        <v>55</v>
+      </c>
+      <c r="N18" s="16">
         <v>75000</v>
       </c>
       <c r="O18" s="8" t="s">
@@ -1440,16 +3011,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="8">
+        <v>56</v>
+      </c>
+      <c r="B19" s="16">
         <v>25000</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F19" s="8">
         <v>20</v>
@@ -1458,27 +3029,27 @@
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="8">
         <v>10</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="8">
+        <v>59</v>
+      </c>
+      <c r="B20" s="16">
         <v>15000</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="8">
         <v>70</v>
@@ -1487,32 +3058,32 @@
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J20" s="8">
         <v>20</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
+        <v>50</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="8">
+        <v>63</v>
+      </c>
+      <c r="B21" s="16">
         <v>5000</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F21" s="8">
         <v>30</v>
@@ -1521,27 +3092,27 @@
         <v>15</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="N21" s="8">
+        <v>65</v>
+      </c>
+      <c r="N21" s="16">
         <v>25000</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="8">
+        <v>66</v>
+      </c>
+      <c r="B22" s="16">
         <v>100</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F22" s="8">
         <v>60</v>
@@ -1550,25 +3121,25 @@
         <v>20</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J22" s="22"/>
       <c r="K22" s="22"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E23" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F23" s="8">
         <v>10</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="8">
+        <v>69</v>
+      </c>
+      <c r="J23" s="16">
         <v>12500</v>
       </c>
       <c r="K23" s="8" t="s">
@@ -1576,33 +3147,33 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
       <c r="E24" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F24" s="8">
         <v>15</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" s="8">
+        <v>72</v>
+      </c>
+      <c r="J24" s="16">
         <v>2500</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B25" s="8">
         <v>-25000</v>
@@ -1611,9 +3182,9 @@
         <v>11</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25" s="8">
+        <v>74</v>
+      </c>
+      <c r="J25" s="16">
         <v>10000</v>
       </c>
       <c r="K25" s="8" t="s">
@@ -1621,15 +3192,15 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I27" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
+      <c r="I27" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I28" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J28" s="8">
         <v>-25000</v>
@@ -1640,7 +3211,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I29" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J29" s="8">
         <v>-50000</v>
@@ -1650,33 +3221,35 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A11:C11"/>
+  <mergeCells count="20">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="I27:K27"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="I22:K22"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="I10:K10"/>
     <mergeCell ref="M4:O4"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="M16:O16"/>
     <mergeCell ref="M12:O12"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="I4:K4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C9 C12 C13 C16 C17 C18 C19 C20 C21 C22 G14 G15 G16 G19 G20 G21 G22 G23 G24 K11 K12 K13 K14 K17 K18 K19 K20 K23 K24 K25 O5 O6 O9 O10 O13 O14 O17 O18 O21" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C9 C12:C13 C16:C22 G14:G16 G19:G24 K11:K14 K17:K20 K23:K25 O5:O6 O9:O10 O13:O14 O17:O18 O21" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1 час,12 часов,24 часа,Неделя,Рандом"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1701,31 +3274,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="26">
+        <f>SUM(R3:R6)</f>
+        <v>0</v>
+      </c>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="Q2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="18">
-        <f>SUM(R3:R6)</f>
-        <v>0</v>
-      </c>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="Q2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="Q3" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R3" s="10">
         <f>SUM(C6,C7,C10,C13,C14,C17,C18,C19,C20,C21,C22,C23,C26)</f>
@@ -1737,40 +3310,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="N4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q4" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="R4" s="10">
         <f>SUM(G6,G7,G8,G9,G10,G11,G12,G15,G16,G17,G20,G21,G22,G23,G24,G25)</f>
@@ -1778,28 +3351,28 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="E5" s="13" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="I5" s="13" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="I5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="M5" s="13" t="s">
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="M5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
       <c r="Q5" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="R5" s="10">
         <f>SUM(K6,K7,K8,K9,K12,K13,K14,K15,K18,K19,K20,K21,K24,K25,K26,K29,K30)</f>
@@ -1852,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R6" s="10">
         <f>SUM(O6,O7,O10,O11,O14,O15,O18,O19,O22)</f>
@@ -1930,11 +3503,11 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
       <c r="E9" s="7" t="str">
         <f>Настройки!E8</f>
         <v>Видео кружок</v>
@@ -1957,11 +3530,11 @@
         <f>J9 * Настройки!J8 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="str">
@@ -2010,11 +3583,11 @@
         <f>F11 * Настройки!F10 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
       <c r="M11" s="7" t="str">
         <f>Настройки!M10</f>
         <v>Журналист (НьюзON)</v>
@@ -2028,11 +3601,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
       <c r="E12" s="7" t="str">
         <f>Настройки!E11</f>
         <v>GIF-анимация</v>
@@ -2079,11 +3652,11 @@
         <f>J13 * Настройки!J12 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="str">
@@ -2097,11 +3670,11 @@
         <f>B14 * Настройки!B13 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
       <c r="I14" s="7" t="str">
         <f>Настройки!I13</f>
         <v>Хит (4 лайка)</v>
@@ -2150,7 +3723,7 @@
       </c>
       <c r="M15" s="7" t="str">
         <f>Настройки!M14</f>
-        <v>Сваха (BBS)</v>
+        <v>«Амбассадор Любви»</v>
       </c>
       <c r="N15" s="11">
         <v>0</v>
@@ -2161,11 +3734,11 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
+      <c r="A16" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
       <c r="E16" s="7" t="str">
         <f>Настройки!E15</f>
         <v>Рецензент (Видео+Текст)</v>
@@ -2201,16 +3774,16 @@
         <f>F17 * Настройки!F16 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="M17" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="M17" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="str">
@@ -2259,11 +3832,11 @@
         <f>B19 * Настройки!B18 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
       <c r="I19" s="7" t="str">
         <f>Настройки!I18</f>
         <v>Центр (20 ответов тебе)</v>
@@ -2356,11 +3929,11 @@
         <f>J21 * Настройки!J20 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M21" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
+      <c r="M21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="str">
@@ -2420,11 +3993,11 @@
         <f>F23 * Настройки!F22 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I23" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
+      <c r="I23" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E24" s="7" t="str">
@@ -2451,11 +4024,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
       <c r="E25" s="7" t="str">
         <f>Настройки!E24</f>
         <v>Гифошная (10 гиф)</v>
@@ -2504,11 +4077,11 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I28" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
+      <c r="I28" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I29" s="7" t="str">
@@ -2545,11 +4118,6 @@
     <mergeCell ref="C1:D2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="M9:O9"/>
     <mergeCell ref="M5:O5"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A25:C25"/>
@@ -2558,6 +4126,11 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="M21:O21"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="M9:O9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/Pulse_Economy_V5.xlsx
+++ b/Pulse_Economy_V5.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bot_2\telegram_bot2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAEBDE7-3490-4F15-819A-DC683A0A1286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64B0157-E9E3-4788-B857-3DA123034F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Настройки" sheetId="1" r:id="rId1"/>
     <sheet name="Симулятор" sheetId="2" r:id="rId2"/>
+    <sheet name="Квесты И Сезоны" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1489,7 +1490,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="131">
   <si>
     <t>ГЛОБАЛЬНАЯ БАЗА (1x) =</t>
   </si>
@@ -1801,6 +1802,132 @@
   <si>
     <t>🌍 БИОМЫ К ЭТОМУ ИВЕНТУ</t>
   </si>
+  <si>
+    <t>Когда биом ПлюсON во тьме (02-06), стань тем, кто даст развернутый ответ.</t>
+  </si>
+  <si>
+    <t>Ночной Дозор</t>
+  </si>
+  <si>
+    <t>🗺 Сезон 1 (Золото)</t>
+  </si>
+  <si>
+    <t>Спустись в архивы и вдохни жизнь в дискуссию, мертвую двое суток.</t>
+  </si>
+  <si>
+    <t>Некромантия</t>
+  </si>
+  <si>
+    <t>🗺 Сезон 1 (Серебро)</t>
+  </si>
+  <si>
+    <t>Варвары кричат, а мудрецы благодарят. Покажи манеры в длинной речи.</t>
+  </si>
+  <si>
+    <t>Слово Древних</t>
+  </si>
+  <si>
+    <t>🗺 Сезон 1 (Бронза)</t>
+  </si>
+  <si>
+    <t>Говорят, если заговорить с миром, когда часы показывают идеальное отражение...</t>
+  </si>
+  <si>
+    <t>Ритуал Времени</t>
+  </si>
+  <si>
+    <t>Неделя</t>
+  </si>
+  <si>
+    <t>Пожертвовать в Реактор суммарно 500 💎</t>
+  </si>
+  <si>
+    <t>Меценат недели</t>
+  </si>
+  <si>
+    <t>🟡 Еженедельные</t>
+  </si>
+  <si>
+    <t>Выполнить 20 ежедневных квестов (дейликов) за неделю</t>
+  </si>
+  <si>
+    <t>Марафонец</t>
+  </si>
+  <si>
+    <t>Текст в Главном чате вызвал дискуссию (4 ответа)</t>
+  </si>
+  <si>
+    <t>Лидер мнений</t>
+  </si>
+  <si>
+    <t>🟣 Сложные</t>
+  </si>
+  <si>
+    <t>Ваш мем в МемасON собрал 7+ реакций от разных людей</t>
+  </si>
+  <si>
+    <t>Топовый мем</t>
+  </si>
+  <si>
+    <t>Ваше голосовое сообщение или кружок собрал 5+ реакций</t>
+  </si>
+  <si>
+    <t>Звезда эфира</t>
+  </si>
+  <si>
+    <t>Записать 1 Video Note (кружочек лицом)</t>
+  </si>
+  <si>
+    <t>Кружок по интересам</t>
+  </si>
+  <si>
+    <t>🔵 Средние</t>
+  </si>
+  <si>
+    <t>Записать 1 голосовое сообщение (длиннее 10 секунд)</t>
+  </si>
+  <si>
+    <t>Голос чата</t>
+  </si>
+  <si>
+    <t>Написать осмысленное сообщение от 20 до 40 слов</t>
+  </si>
+  <si>
+    <t>Длинная мысль</t>
+  </si>
+  <si>
+    <t>Поставить 3 реакции ❤️ на чужих животных в ПИТОМЦЫ</t>
+  </si>
+  <si>
+    <t>Котопес</t>
+  </si>
+  <si>
+    <t>🟢 Простые</t>
+  </si>
+  <si>
+    <t>Поставить 5 любых реакций на чужие сообщения</t>
+  </si>
+  <si>
+    <t>Эмоциональный отклик</t>
+  </si>
+  <si>
+    <t>Написать первое сообщение в чат до 08:00 МСК</t>
+  </si>
+  <si>
+    <t>Жаворонок</t>
+  </si>
+  <si>
+    <t>Награда (💎)</t>
+  </si>
+  <si>
+    <t>Описание (Примечание)</t>
+  </si>
+  <si>
+    <t>Название Квеста</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
 </sst>
 </file>
 
@@ -1810,7 +1937,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.000\ \_xd83d_\_xdc8e_"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1918,8 +2045,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF27AE60"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1968,6 +2101,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2980B9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1996,7 +2134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2025,26 +2163,41 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2530,22 +2683,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
       <c r="D1" s="1">
         <v>2E-3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -2586,26 +2739,26 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="E4" s="18" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="E4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="I4" s="18" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="I4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="M4" s="18" t="s">
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="M4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2704,11 +2857,11 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
       <c r="E8" s="7" t="s">
         <v>24</v>
       </c>
@@ -2727,11 +2880,11 @@
       <c r="K8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -2772,11 +2925,11 @@
       <c r="G10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
       <c r="M10" s="7" t="s">
         <v>31</v>
       </c>
@@ -2788,11 +2941,11 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
       <c r="E11" s="7" t="s">
         <v>33</v>
       </c>
@@ -2831,11 +2984,11 @@
       <c r="K12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -2847,11 +3000,11 @@
       <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
       <c r="I13" s="7" t="s">
         <v>39</v>
       </c>
@@ -2901,11 +3054,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
       <c r="E15" s="7" t="s">
         <v>44</v>
       </c>
@@ -2935,16 +3088,16 @@
       <c r="G16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="M16" s="18" t="s">
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="M16" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -2985,11 +3138,11 @@
       <c r="C18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
       <c r="I18" s="7" t="s">
         <v>54</v>
       </c>
@@ -3066,11 +3219,11 @@
       <c r="K20" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="18" t="s">
+      <c r="M20" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -3120,11 +3273,11 @@
       <c r="G22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E23" s="7" t="s">
@@ -3147,11 +3300,11 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
       <c r="E24" s="7" t="s">
         <v>71</v>
       </c>
@@ -3192,11 +3345,11 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I28" s="7" t="s">
@@ -3222,6 +3375,17 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="M20:O20"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="I27:K27"/>
     <mergeCell ref="E4:G4"/>
@@ -3231,17 +3395,6 @@
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="I10:K10"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="I4:K4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="C9 C12:C13 C16:C22 G14:G16 G19:G24 K11:K14 K17:K20 K23:K25 O5:O6 O9:O10 O13:O14 O17:O18 O21" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3277,18 +3430,18 @@
       <c r="A1" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="26">
         <f>SUM(R3:R6)</f>
         <v>0</v>
       </c>
-      <c r="D1" s="24"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="Q2" s="3" t="s">
         <v>78</v>
       </c>
@@ -3351,26 +3504,26 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="E5" s="18" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="E5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="I5" s="18" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="I5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="M5" s="18" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="M5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
       <c r="Q5" s="9" t="s">
         <v>84</v>
       </c>
@@ -3503,11 +3656,11 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
       <c r="E9" s="7" t="str">
         <f>Настройки!E8</f>
         <v>Видео кружок</v>
@@ -3530,11 +3683,11 @@
         <f>J9 * Настройки!J8 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="str">
@@ -3583,11 +3736,11 @@
         <f>F11 * Настройки!F10 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
       <c r="M11" s="7" t="str">
         <f>Настройки!M10</f>
         <v>Журналист (НьюзON)</v>
@@ -3601,11 +3754,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
       <c r="E12" s="7" t="str">
         <f>Настройки!E11</f>
         <v>GIF-анимация</v>
@@ -3652,11 +3805,11 @@
         <f>J13 * Настройки!J12 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="str">
@@ -3670,11 +3823,11 @@
         <f>B14 * Настройки!B13 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
       <c r="I14" s="7" t="str">
         <f>Настройки!I13</f>
         <v>Хит (4 лайка)</v>
@@ -3734,11 +3887,11 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
       <c r="E16" s="7" t="str">
         <f>Настройки!E15</f>
         <v>Рецензент (Видео+Текст)</v>
@@ -3774,16 +3927,16 @@
         <f>F17 * Настройки!F16 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="M17" s="18" t="s">
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="M17" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="str">
@@ -3832,11 +3985,11 @@
         <f>B19 * Настройки!B18 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
       <c r="I19" s="7" t="str">
         <f>Настройки!I18</f>
         <v>Центр (20 ответов тебе)</v>
@@ -3929,11 +4082,11 @@
         <f>J21 * Настройки!J20 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="M21" s="18" t="s">
+      <c r="M21" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="str">
@@ -3993,11 +4146,11 @@
         <f>F23 * Настройки!F22 * Настройки!$D$1</f>
         <v>0</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="E24" s="7" t="str">
@@ -4024,11 +4177,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
       <c r="E25" s="7" t="str">
         <f>Настройки!E24</f>
         <v>Гифошная (10 гиф)</v>
@@ -4077,11 +4230,11 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="I29" s="7" t="str">
@@ -4111,13 +4264,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="M5:O5"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A25:C25"/>
@@ -4131,8 +4277,302 @@
     <mergeCell ref="I17:K17"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="M9:O9"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2744AF57-9288-44CF-92A4-CC69E64E6BD6}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="30">
+        <v>2</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="30">
+        <v>1</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="30">
+        <v>1</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="30">
+        <v>3</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="30">
+        <v>3</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="30">
+        <v>5</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="30">
+        <v>12</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="30">
+        <v>15</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="30">
+        <v>15</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="30">
+        <v>40</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="30">
+        <v>50</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="30">
+        <v>15</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="30">
+        <v>10</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="30">
+        <v>40</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="30">
+        <v>150</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>